--- a/data/trans_orig/IP16B05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16B05-Clase-trans_orig.xlsx
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20655</t>
+          <t>21503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40343</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
